--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,10 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>需要找PM
-一樣的狀況
-所以....
-可以嗎???</t>
+          <t>需要找PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -1,34 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="612" yWindow="516" windowWidth="21792" windowHeight="7032"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>事項編號</t>
+  </si>
+  <si>
+    <t>工作狀態</t>
+  </si>
+  <si>
+    <t>BUILD</t>
+  </si>
+  <si>
+    <t>NO.</t>
+  </si>
+  <si>
+    <t>事項描述</t>
+  </si>
+  <si>
+    <t>回報狀況</t>
+  </si>
+  <si>
+    <t>起始日期</t>
+  </si>
+  <si>
+    <t>經手人員</t>
+  </si>
+  <si>
+    <t>Station</t>
+  </si>
+  <si>
+    <t>W-001</t>
+  </si>
+  <si>
+    <t>Ongoing</t>
+  </si>
+  <si>
+    <t>TS2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>需要找PM</t>
+  </si>
+  <si>
+    <t>2026-09-24 00:00:00</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>AOT</t>
+  </si>
+  <si>
+    <t>W-002</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>test 123</t>
+  </si>
+  <si>
+    <t>做了很多測試</t>
+  </si>
+  <si>
+    <t>2026-09-25 00:00:00</t>
+  </si>
+  <si>
+    <t>不知名人士</t>
+  </si>
+  <si>
+    <t>System_FT</t>
+  </si>
+  <si>
+    <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +136,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,156 +435,99 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>事項編號</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>工作狀態</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>BUILD</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>NO.</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>事項描述</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>回報狀況</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>起始日期</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>經手人員</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Station</t>
-        </is>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>W-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>需要找PM</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>W-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>test 123</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>做了很多測試</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>不知名人士</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>System_FT</t>
-        </is>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -1,123 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="612" yWindow="516" windowWidth="21792" windowHeight="7032"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>事項編號</t>
-  </si>
-  <si>
-    <t>工作狀態</t>
-  </si>
-  <si>
-    <t>BUILD</t>
-  </si>
-  <si>
-    <t>NO.</t>
-  </si>
-  <si>
-    <t>事項描述</t>
-  </si>
-  <si>
-    <t>回報狀況</t>
-  </si>
-  <si>
-    <t>起始日期</t>
-  </si>
-  <si>
-    <t>經手人員</t>
-  </si>
-  <si>
-    <t>Station</t>
-  </si>
-  <si>
-    <t>W-001</t>
-  </si>
-  <si>
-    <t>Ongoing</t>
-  </si>
-  <si>
-    <t>TS2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>需要找PM</t>
-  </si>
-  <si>
-    <t>2026-09-24 00:00:00</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>AOT</t>
-  </si>
-  <si>
-    <t>W-002</t>
-  </si>
-  <si>
-    <t>Resolved</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>test 123</t>
-  </si>
-  <si>
-    <t>做了很多測試</t>
-  </si>
-  <si>
-    <t>2026-09-25 00:00:00</t>
-  </si>
-  <si>
-    <t>不知名人士</t>
-  </si>
-  <si>
-    <t>System_FT</t>
-  </si>
-  <si>
-    <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,18 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -435,99 +408,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>事項編號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>工作狀態</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>事項描述</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>回報狀況</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>起始日期</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>經手人員</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>W-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>需要找PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>test 123</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>做了很多測試</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>不知名人士</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>System_FT</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,45 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>System_FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>新增一個測試</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AOT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -589,7 +589,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>AOT</t>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,11 @@
           <t>新增一個測試</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -595,6 +599,45 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ttttttttttt</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>AOT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,69 +575,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>新增一個測試</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
+          <t>PM 要求要重測 老闆最大.....</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>W-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ttttttttttt</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
         <is>
           <t>AOT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,14 +583,61 @@
           <t>PM 要求要重測 老闆最大.....</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>只是測試而已</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>AOT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,16 +630,63 @@
           <t>只是測試而已</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>AOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>請夜班幫幫忙</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SYSTEM_FT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-002</t>
+          <t>W-003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,39 +528,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>test 123</t>
+          <t>PM 要求要重測 老闆最大.....</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>做了很多測試</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-25 00:00:00</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>不知名人士</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>System_FT</t>
+          <t>AOT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-003</t>
+          <t>W-004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PM 要求要重測 老闆最大.....</t>
+          <t>只是測試而已</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W-004</t>
+          <t>W-005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>只是測試而已</t>
+          <t>請夜班幫幫忙</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -646,45 +646,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>請夜班幫幫忙</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W-001</t>
+          <t>W-003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,27 +481,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
+          <t>PM 要求要重測 老闆最大.....</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>需要找PM</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:00:00</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-003</t>
+          <t>W-004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PM 要求要重測 老闆最大.....</t>
+          <t>只是測試而已</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-004</t>
+          <t>W-005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>只是測試而已</t>
+          <t>請夜班幫幫忙</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,53 +599,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>W-005</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>請夜班幫幫忙</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,53 +554,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>AOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>W-005</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>請夜班幫幫忙</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SYSTEM_FT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,49 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>AOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W-005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>測試中</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W-003</t>
+          <t>W-004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,12 +481,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PM 要求要重測 老闆最大.....</t>
+          <t>只是測試而已</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-004</t>
+          <t>W-005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>只是測試而已</t>
+          <t>測試中</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,53 +548,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>W-005</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TS2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>測試中</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>無資料測試一下</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,45 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W-006</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AOT FAIL，需要幫忙追一下</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AOT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,14 +583,61 @@
           <t>AOT FAIL，需要幫忙追一下</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W-007</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TTEST</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>AOT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-006</t>
+          <t>W-007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>TS3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AOT FAIL，需要幫忙追一下</t>
+          <t>TTEST</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,45 +599,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>W-007</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TTEST</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
         <is>
           <t>AOT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W-004</t>
+          <t>W-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>只是測試而已</t>
+          <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>無資料測試一下</t>
+          <t>需要找PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-24 00:00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-005</t>
+          <t>W-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,39 +528,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>測試中</t>
+          <t>test 123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>做了很多測試</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25 00:00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>不知名人士</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MGMT_JTAG</t>
+          <t>System_FT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-007</t>
+          <t>W-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,32 +575,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TTEST</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
+          <t>TEST_追踨此台是否CPU那模沒撕</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>SYSTEM_FT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,18 +583,61 @@
           <t>TEST_追踨此台是否CPU那模沒撕</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[TEST]用來做AUTO的機台, 暫時先不理. KEEP一下</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,14 +630,61 @@
           <t>[TEST]用來做AUTO的機台, 暫時先不理. KEEP一下</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>什麼都不加會如何</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -677,14 +677,26 @@
           <t>什麼都不加會如何</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W-001</t>
+          <t>W-002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,86 +481,86 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>test kdflsdkjfdskljfsdjf jsdjflsdkj我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是我是</t>
+          <t>test 123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>需要找PM</t>
+          <t>做了很多測試</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:00:00</t>
+          <t>2026-09-25 00:00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>不知名人士</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>System_FT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-002</t>
+          <t>W-003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>TS3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>test 123</t>
+          <t>TEST_追踨此台是否CPU那模沒撕</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>做了很多測試</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-25 00:00:00</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>不知名人士</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>System_FT</t>
+          <t>SYSTEM_FT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-003</t>
+          <t>W-004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TEST_追踨此台是否CPU那模沒撕</t>
+          <t>[TEST]用來做AUTO的機台, 暫時先不理. KEEP一下</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -600,14 +600,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SYSTEM_FT</t>
+          <t>無資料</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W-004</t>
+          <t>W-005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[TEST]用來做AUTO的機台, 暫時先不理. KEEP一下</t>
+          <t>什麼都不加會如何</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -646,53 +646,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>什麼都不加會如何</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>無資料</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,45 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>無資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W-006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,16 +677,63 @@
           <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W-007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COU 100 —&gt; 離型紙未移除</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MGMT_FT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,14 +724,61 @@
           <t>COU 100 —&gt; 離型紙未移除</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>MGMT_FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W-008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CPU 100度 —》離型紙未移除</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>MGMT_FT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,16 +771,63 @@
           <t>CPU 100度 —》離型紙未移除</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>MGMT_FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W-009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CPU 100度 —》離型紙未移除</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,45 +789,6 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>MGMT_FT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>W-009</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CPU 100度 —》離型紙未移除</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,53 +740,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>MGMT_FT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>W-008</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CPU 100度 —》離型紙未移除</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>MGMT_FT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,53 +695,6 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>W-007</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COU 100 —&gt; 離型紙未移除</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MGMT_FT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,45 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>MGMT_JTAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W-007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>63465147980055</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>錯誤3333</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,14 +724,61 @@
           <t>錯誤3333</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>MGMT_JTAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W-008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>單版</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>63465147980055</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W-007</t>
+          <t>W-008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TS3</t>
+          <t>單版</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>錯誤3333</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -740,45 +740,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>MGMT_JTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>W-008</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>單版</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>63465147980055</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W-005</t>
+          <t>W-006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TS3</t>
+          <t>TS2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>什麼都不加會如何</t>
+          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -647,14 +647,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W-006</t>
+          <t>W-008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>單版</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>63465147980055</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -693,53 +693,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>MGMT_JTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>W-008</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>單版</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>63465147980055</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-004</t>
+          <t>W-006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TS3</t>
+          <t>TS2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[TEST]用來做AUTO的機台, 暫時先不理. KEEP一下</t>
+          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -600,14 +600,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W-006</t>
+          <t>W-008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>單版</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>63465147980055</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -646,53 +646,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>MGMT_JTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W-008</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>單版</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>63465147980055</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,45 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>MGMT_JTAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W-009</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>livefish問題: 1.手動開機 2. 換站重測 3. 回報Jetz</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SYSTEM_FT</t>
         </is>
       </c>
     </row>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-003</t>
+          <t>W-006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TS3</t>
+          <t>TS2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TEST_追踨此台是否CPU那模沒撕</t>
+          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,14 +553,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SYSTEM_FT</t>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-006</t>
+          <t>W-008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>單版</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>63465147980055</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W-008</t>
+          <t>W-009</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>單版</t>
+          <t>TS3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>63465147980055</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>livefish問題: 1.手動開機 2. 換站重測 3. 回報Jetz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -646,45 +646,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>MGMT_JTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W-009</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>livefish問題: 1.手動開機 2. 換站重測 3. 回報Jetz</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
         </is>

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>9/28 已回報給Eric</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/Work_item.xlsx
+++ b/Work_item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W-002</t>
+          <t>W-006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,39 +481,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>test 123</t>
+          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>做了很多測試</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-25 00:00:00</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>不知名人士</t>
+          <t>無資料</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>System_FT</t>
+          <t>MGMT_JTAG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W-006</t>
+          <t>W-008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>單版</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>63465147980055</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fail on step8 : Run Authenticator Win.etf. 10/1 9:35 CPU無法開機--&gt;Still fail        客人會提供vin pg是什麼 NV目前沒更新</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,92 +560,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W-008</t>
+          <t>W-009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>單版</t>
+          <t>TS3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>63465147980055</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>livefish問題: 1.手動開機 2. 換站重測 3. 回報Jetz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>9/28 已回報給Eric</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>無資料</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>MGMT_JTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>W-009</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>livefish問題: 1.手動開機 2. 換站重測 3. 回報Jetz</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>9/28 已回報給Eric</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
         </is>
